--- a/StructureDefinition-specific-finding-observation-profile.xlsx
+++ b/StructureDefinition-specific-finding-observation-profile.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T11:15:53+00:00</t>
+    <t>2026-05-08T09:03:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-specific-finding-observation-profile.xlsx
+++ b/StructureDefinition-specific-finding-observation-profile.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2406" uniqueCount="503">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2407" uniqueCount="503">
   <si>
     <t>Property</t>
   </si>
@@ -51,16 +51,19 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
   </si>
   <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T09:03:17+00:00</t>
+    <t>2026-05-08T09:31:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Generic profile for specific imaging/procedure/clinical findings including mTICI, bleeding volume, carotid stenosis, occlusion and AF/flutter.</t>
+    <t>Observation profile for specific clinical, imaging or procedural findings including mTICI, bleeding volume, carotid stenosis, occlusion and atrial fibrillation/flutter.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -118,9 +121,6 @@
   </si>
   <si>
     <t>Abstract</t>
-  </si>
-  <si>
-    <t>false</t>
   </si>
   <si>
     <t>Derivation</t>
@@ -741,7 +741,7 @@
     <t>Observation.status</t>
   </si>
   <si>
-    <t>registered | preliminary | final | amended +</t>
+    <t>Final registry observation</t>
   </si>
   <si>
     <t>The status of the result value.</t>
@@ -818,7 +818,7 @@
 </t>
   </si>
   <si>
-    <t>Type of observation (code / type)</t>
+    <t>Specific stroke finding</t>
   </si>
   <si>
     <t>Describes what was observed. Sometimes this is called the observation "name".</t>
@@ -862,10 +862,10 @@
 </t>
   </si>
   <si>
-    <t>Who and/or what the observation is about</t>
-  </si>
-  <si>
-    <t>The patient, or group of patients, location, device, organization, procedure or practitioner this observation is about and into whose or what record the observation is placed. If the actual focus of the observation is different from the subject (or a sample of, part, or region of the subject), the `focus` element or the `code` itself specifies the actual focus of the observation.</t>
+    <t>RES-Q registry patient</t>
+  </si>
+  <si>
+    <t>Patient who experienced the index stroke episode represented in this registry dataset.</t>
   </si>
   <si>
     <t>One would expect this element to be a cardinality of 1..1. The only circumstance in which the subject can be missing is when the observation is made by a device that does not know the patient. In this case, the observation SHALL be matched to a patient through some context/channel matching technique, and at this point, the observation should be updated. The subject of an Observation may in some cases be a procedure.  This supports the regulatory inspection use case where observations are captured during inspections of a procedure that is being performed (independent of any particular patient or whether patient related at all).</t>
@@ -916,10 +916,10 @@
 </t>
   </si>
   <si>
-    <t>Healthcare event during which this observation is made</t>
-  </si>
-  <si>
-    <t>The healthcare event  (e.g. a patient and healthcare provider interaction) during which this observation is made.</t>
+    <t>Index stroke encounter</t>
+  </si>
+  <si>
+    <t>Encounter that anchors the clinical fact to the acute stroke episode and hospital pathway.</t>
   </si>
   <si>
     <t>This will typically be the encounter the event occurred within, but some events may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter (e.g. pre-admission laboratory tests).</t>
@@ -1035,7 +1035,7 @@
 CodeableConceptbooleaninteger</t>
   </si>
   <si>
-    <t>Actual result</t>
+    <t>Finding value</t>
   </si>
   <si>
     <t>The information determined as a result of making the observation, if the information has a simple value.</t>
@@ -1206,7 +1206,7 @@
 </t>
   </si>
   <si>
-    <t>Observed body structure</t>
+    <t>Anatomical structure associated with the finding</t>
   </si>
   <si>
     <t>Indicates the body structure on the subject's body where the observation was made (i.e. the target site).</t>
@@ -1820,98 +1820,100 @@
       <c r="A7" t="s" s="2">
         <v>12</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
@@ -2105,10 +2107,10 @@
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
@@ -2190,7 +2192,7 @@
         <v>82</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AG2" t="s" s="2">
         <v>80</v>

--- a/StructureDefinition-specific-finding-observation-profile.xlsx
+++ b/StructureDefinition-specific-finding-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T09:31:23+00:00</t>
+    <t>2026-05-08T10:13:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-specific-finding-observation-profile.xlsx
+++ b/StructureDefinition-specific-finding-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T10:13:17+00:00</t>
+    <t>2026-05-11T15:54:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-specific-finding-observation-profile.xlsx
+++ b/StructureDefinition-specific-finding-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:54:34+00:00</t>
+    <t>2026-05-11T15:54:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-specific-finding-observation-profile.xlsx
+++ b/StructureDefinition-specific-finding-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:54:44+00:00</t>
+    <t>2026-05-12T07:59:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-specific-finding-observation-profile.xlsx
+++ b/StructureDefinition-specific-finding-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T07:59:38+00:00</t>
+    <t>2026-05-12T09:41:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-specific-finding-observation-profile.xlsx
+++ b/StructureDefinition-specific-finding-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T09:41:56+00:00</t>
+    <t>2026-05-12T11:55:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-specific-finding-observation-profile.xlsx
+++ b/StructureDefinition-specific-finding-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T11:55:23+00:00</t>
+    <t>2026-05-13T14:14:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-specific-finding-observation-profile.xlsx
+++ b/StructureDefinition-specific-finding-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:14:43+00:00</t>
+    <t>2026-05-13T15:23:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-specific-finding-observation-profile.xlsx
+++ b/StructureDefinition-specific-finding-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T15:23:44+00:00</t>
+    <t>2026-05-14T08:09:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-specific-finding-observation-profile.xlsx
+++ b/StructureDefinition-specific-finding-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T08:09:55+00:00</t>
+    <t>2026-05-14T08:55:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-specific-finding-observation-profile.xlsx
+++ b/StructureDefinition-specific-finding-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T08:55:50+00:00</t>
+    <t>2026-05-14T09:35:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-specific-finding-observation-profile.xlsx
+++ b/StructureDefinition-specific-finding-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T09:35:04+00:00</t>
+    <t>2026-05-14T11:02:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-specific-finding-observation-profile.xlsx
+++ b/StructureDefinition-specific-finding-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T11:02:20+00:00</t>
+    <t>2026-05-15T10:10:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-specific-finding-observation-profile.xlsx
+++ b/StructureDefinition-specific-finding-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T10:10:20+00:00</t>
+    <t>2026-06-01T07:47:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-specific-finding-observation-profile.xlsx
+++ b/StructureDefinition-specific-finding-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T07:47:29+00:00</t>
+    <t>2026-06-01T10:24:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-specific-finding-observation-profile.xlsx
+++ b/StructureDefinition-specific-finding-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T10:24:12+00:00</t>
+    <t>2026-06-01T10:42:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-specific-finding-observation-profile.xlsx
+++ b/StructureDefinition-specific-finding-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T10:42:50+00:00</t>
+    <t>2026-06-01T12:57:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-specific-finding-observation-profile.xlsx
+++ b/StructureDefinition-specific-finding-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T12:57:35+00:00</t>
+    <t>2026-06-02T10:42:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-specific-finding-observation-profile.xlsx
+++ b/StructureDefinition-specific-finding-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T10:42:43+00:00</t>
+    <t>2026-06-03T07:55:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-specific-finding-observation-profile.xlsx
+++ b/StructureDefinition-specific-finding-observation-profile.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$63</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2407" uniqueCount="503">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2445" uniqueCount="508">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T07:55:03+00:00</t>
+    <t>2026-06-03T14:48:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -282,7 +282,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().ofType(canonical) | %resource.descendants().ofType(uri) | %resource.descendants().ofType(url))) or descendants().where(reference = '#').exists() or descendants().where(ofType(canonical) = '#').exists() or descendants().where(ofType(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.component.code is the same as Observation.code, then Observation.value SHALL NOT be present (the Observation.component.value[x] holds the value). {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}obs-8:bodyStructure SHALL only be present if Observation.bodySite is not present {bodySite.exists() implies bodyStructure.empty()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().ofType(canonical) | %resource.descendants().ofType(uri) | %resource.descendants().ofType(url))) or descendants().where(reference = '#').exists() or descendants().where(ofType(canonical) = '#').exists() or descendants().where(ofType(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.component.code is the same as Observation.code, then Observation.value SHALL NOT be present (the Observation.component.value[x] holds the value). {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}obs-8:bodyStructure SHALL only be present if Observation.bodySite is not present {bodySite.exists() implies bodyStructure.empty()}mtici-value-must-use-mtici-score-vs:If Observation.code is mTICI, valueCodeableConcept must belong to MTiciScoreVS. {code.coding.where(system = 'http://tecnomod-um.org/CodeSystem/specific-finding-cs' and code = 'mtici').exists().not() or value.ofType(CodeableConcept).memberOf('http://tecnomod-um.org/ValueSet/mtici-score-vs')}af-flutter-value-must-use-af-flutter-vs:If Observation.code is atrial fibrillation/flutter, valueCodeableConcept must belong to AtrialFibrillationOrFlutterVS. {code.coding.where(system = 'http://tecnomod-um.org/CodeSystem/specific-finding-cs' and code = 'atrial-fibrillation-flutter').exists().not() or value.ofType(CodeableConcept).memberOf('http://tecnomod-um.org/ValueSet/atrial-fibrillation-or-flutter-vs')}</t>
   </si>
   <si>
     <t>Event</t>
@@ -1055,6 +1055,10 @@
     <t>An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
   </si>
   <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
     <t>obs-7
 obs-6</t>
   </si>
@@ -1069,6 +1073,18 @@
   </si>
   <si>
     <t>363714003 |Interprets|</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>Coded finding value, such as mTICI score or atrial fibrillation/flutter status</t>
+  </si>
+  <si>
+    <t>http://tecnomod-um.org/ValueSet/specific-finding-value-codeableconcept-vs</t>
   </si>
   <si>
     <t>Observation.dataAbsentReason</t>
@@ -1931,7 +1947,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP62"/>
+  <dimension ref="A1:AP63"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="40.0234375" customWidth="true" bestFit="true"/>
@@ -1959,7 +1975,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="54.6171875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="59.41796875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="60.96875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
@@ -5703,7 +5719,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
         <v>322</v>
       </c>
@@ -5780,16 +5796,14 @@
         <v>82</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC32" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>328</v>
+      </c>
+      <c r="AC32" s="2"/>
       <c r="AD32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>82</v>
+        <v>145</v>
       </c>
       <c r="AF32" t="s" s="2">
         <v>322</v>
@@ -5801,7 +5815,7 @@
         <v>94</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>106</v>
@@ -5813,26 +5827,28 @@
         <v>82</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="C33" s="2"/>
+        <v>322</v>
+      </c>
+      <c r="C33" t="s" s="2">
+        <v>335</v>
+      </c>
       <c r="D33" t="s" s="2">
         <v>82</v>
       </c>
@@ -5850,22 +5866,22 @@
         <v>82</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="K33" t="s" s="2">
         <v>243</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -5892,11 +5908,9 @@
       <c r="X33" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="Y33" t="s" s="2">
-        <v>338</v>
-      </c>
+      <c r="Y33" s="2"/>
       <c r="Z33" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>82</v>
@@ -5914,7 +5928,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>333</v>
+        <v>322</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5923,7 +5937,7 @@
         <v>94</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>340</v>
+        <v>329</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>106</v>
@@ -5935,35 +5949,35 @@
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>82</v>
+        <v>330</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>139</v>
+        <v>331</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>82</v>
+        <v>333</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>343</v>
+        <v>82</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>82</v>
@@ -5978,16 +5992,16 @@
         <v>243</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -6015,10 +6029,10 @@
         <v>259</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>82</v>
@@ -6036,16 +6050,16 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>82</v>
+        <v>345</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>106</v>
@@ -6057,28 +6071,28 @@
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>350</v>
+        <v>82</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>351</v>
+        <v>139</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>353</v>
+        <v>82</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>82</v>
+        <v>348</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6097,19 +6111,19 @@
         <v>82</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>355</v>
+        <v>243</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -6134,13 +6148,13 @@
         <v>82</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>82</v>
+        <v>259</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>82</v>
+        <v>353</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>82</v>
+        <v>354</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>82</v>
@@ -6158,7 +6172,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6179,24 +6193,24 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>82</v>
+        <v>355</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>82</v>
+        <v>358</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6207,7 +6221,7 @@
         <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>82</v>
@@ -6219,18 +6233,20 @@
         <v>82</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>243</v>
+        <v>360</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="N36" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="N36" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>82</v>
       </c>
@@ -6254,13 +6270,13 @@
         <v>82</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>366</v>
+        <v>82</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>367</v>
+        <v>82</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>368</v>
+        <v>82</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>82</v>
@@ -6278,16 +6294,16 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>369</v>
+        <v>82</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>106</v>
@@ -6299,24 +6315,24 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>370</v>
+        <v>82</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>373</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6330,7 +6346,7 @@
         <v>94</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>82</v>
@@ -6339,16 +6355,16 @@
         <v>82</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>375</v>
+        <v>243</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6374,13 +6390,13 @@
         <v>82</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>82</v>
+        <v>371</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>82</v>
+        <v>372</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>82</v>
+        <v>373</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>82</v>
@@ -6398,7 +6414,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6407,7 +6423,7 @@
         <v>94</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>106</v>
@@ -6419,19 +6435,19 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>82</v>
+        <v>375</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>82</v>
+        <v>376</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>82</v>
+        <v>378</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
         <v>379</v>
       </c>
@@ -6450,7 +6466,7 @@
         <v>94</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>82</v>
@@ -6459,20 +6475,18 @@
         <v>82</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>243</v>
+        <v>380</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="O38" t="s" s="2">
         <v>383</v>
       </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>82</v>
       </c>
@@ -6496,13 +6510,13 @@
         <v>82</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>366</v>
+        <v>82</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>384</v>
+        <v>82</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>385</v>
+        <v>82</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>82</v>
@@ -6529,7 +6543,7 @@
         <v>94</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>82</v>
+        <v>374</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>106</v>
@@ -6544,10 +6558,10 @@
         <v>82</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>386</v>
+        <v>82</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>82</v>
@@ -6555,10 +6569,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6581,18 +6595,20 @@
         <v>82</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>389</v>
+        <v>243</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="O39" s="2"/>
+        <v>387</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>388</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
       </c>
@@ -6616,13 +6632,13 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>82</v>
+        <v>371</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>82</v>
+        <v>389</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>82</v>
+        <v>390</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
@@ -6640,7 +6656,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6652,7 +6668,7 @@
         <v>82</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>393</v>
+        <v>106</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>82</v>
@@ -6661,24 +6677,24 @@
         <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>394</v>
+        <v>82</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>397</v>
+        <v>82</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6701,16 +6717,16 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6760,7 +6776,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6772,7 +6788,7 @@
         <v>82</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>106</v>
+        <v>398</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>82</v>
@@ -6781,24 +6797,24 @@
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>406</v>
+        <v>402</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6809,7 +6825,7 @@
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>82</v>
@@ -6821,20 +6837,18 @@
         <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>186</v>
+        <v>404</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>411</v>
-      </c>
+        <v>407</v>
+      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>82</v>
       </c>
@@ -6882,19 +6896,19 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>412</v>
+        <v>106</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>82</v>
@@ -6903,24 +6917,24 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>82</v>
+        <v>408</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>82</v>
+        <v>411</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6931,7 +6945,7 @@
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>82</v>
@@ -6943,16 +6957,20 @@
         <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>191</v>
+        <v>413</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
+        <v>414</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>416</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
       </c>
@@ -7000,19 +7018,19 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>193</v>
+        <v>412</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>194</v>
+        <v>82</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>82</v>
+        <v>417</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>82</v>
@@ -7024,10 +7042,10 @@
         <v>82</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>82</v>
+        <v>418</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>195</v>
+        <v>419</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>82</v>
@@ -7035,21 +7053,21 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>154</v>
+        <v>82</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>82</v>
@@ -7061,17 +7079,15 @@
         <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>141</v>
+        <v>190</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7120,19 +7136,19 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>82</v>
+        <v>194</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>147</v>
+        <v>82</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>82</v>
@@ -7155,14 +7171,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>201</v>
+        <v>154</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7175,26 +7191,24 @@
         <v>82</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
         <v>141</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="N44" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="O44" t="s" s="2">
-        <v>158</v>
-      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>82</v>
       </c>
@@ -7242,7 +7256,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7269,7 +7283,7 @@
         <v>82</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>139</v>
+        <v>195</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>82</v>
@@ -7277,42 +7291,46 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>82</v>
+        <v>201</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>419</v>
+        <v>141</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>420</v>
+        <v>202</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
+        <v>203</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>82</v>
       </c>
@@ -7360,19 +7378,19 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>418</v>
+        <v>204</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>422</v>
+        <v>82</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>106</v>
+        <v>147</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>82</v>
@@ -7384,10 +7402,10 @@
         <v>82</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>413</v>
+        <v>82</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>423</v>
+        <v>139</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>82</v>
@@ -7395,10 +7413,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7421,7 +7439,7 @@
         <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="L46" t="s" s="2">
         <v>425</v>
@@ -7478,7 +7496,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7487,7 +7505,7 @@
         <v>94</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>106</v>
@@ -7502,10 +7520,10 @@
         <v>82</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>82</v>
@@ -7513,10 +7531,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7539,13 +7557,13 @@
         <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>243</v>
+        <v>424</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7572,13 +7590,13 @@
         <v>82</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>259</v>
+        <v>82</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>431</v>
+        <v>82</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>432</v>
+        <v>82</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>82</v>
@@ -7596,7 +7614,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7605,7 +7623,7 @@
         <v>94</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>82</v>
+        <v>427</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>106</v>
@@ -7620,10 +7638,10 @@
         <v>82</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>82</v>
@@ -7631,10 +7649,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7660,17 +7678,13 @@
         <v>243</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="M48" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>438</v>
-      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>82</v>
       </c>
@@ -7694,13 +7708,13 @@
         <v>82</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
@@ -7718,7 +7732,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7739,13 +7753,13 @@
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>441</v>
+        <v>82</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>442</v>
+        <v>418</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>352</v>
+        <v>438</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>82</v>
@@ -7753,10 +7767,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7767,7 +7781,7 @@
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>82</v>
@@ -7782,16 +7796,16 @@
         <v>243</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -7816,13 +7830,13 @@
         <v>82</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>366</v>
+        <v>248</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
@@ -7840,13 +7854,13 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>82</v>
@@ -7861,13 +7875,13 @@
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>82</v>
@@ -7875,10 +7889,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7889,7 +7903,7 @@
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>82</v>
@@ -7901,17 +7915,19 @@
         <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="N50" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -7936,13 +7952,13 @@
         <v>82</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>82</v>
+        <v>371</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>82</v>
+        <v>453</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>82</v>
+        <v>454</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>82</v>
@@ -7960,13 +7976,13 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>82</v>
@@ -7981,13 +7997,13 @@
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>82</v>
+        <v>446</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>82</v>
+        <v>447</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>455</v>
+        <v>357</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>82</v>
@@ -7995,10 +8011,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8021,16 +8037,18 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" s="2"/>
+      <c r="O51" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>82</v>
       </c>
@@ -8078,7 +8096,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8087,7 +8105,7 @@
         <v>94</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>422</v>
+        <v>82</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>106</v>
@@ -8102,7 +8120,7 @@
         <v>82</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>413</v>
+        <v>82</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>460</v>
@@ -8127,7 +8145,7 @@
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>82</v>
@@ -8136,7 +8154,7 @@
         <v>82</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
         <v>462</v>
@@ -8147,9 +8165,7 @@
       <c r="M52" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="N52" t="s" s="2">
-        <v>465</v>
-      </c>
+      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8204,10 +8220,10 @@
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>82</v>
+        <v>427</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>106</v>
@@ -8222,10 +8238,10 @@
         <v>82</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>466</v>
+        <v>418</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>209</v>
+        <v>465</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>82</v>
@@ -8233,10 +8249,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8259,16 +8275,16 @@
         <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="M53" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>471</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8318,7 +8334,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8342,10 +8358,10 @@
         <v>82</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>472</v>
+        <v>209</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>82</v>
@@ -8353,10 +8369,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8379,7 +8395,7 @@
         <v>95</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>186</v>
+        <v>473</v>
       </c>
       <c r="L54" t="s" s="2">
         <v>474</v>
@@ -8390,9 +8406,7 @@
       <c r="N54" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="O54" t="s" s="2">
-        <v>477</v>
-      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>82</v>
       </c>
@@ -8440,7 +8454,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8449,7 +8463,7 @@
         <v>81</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>261</v>
+        <v>82</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>106</v>
@@ -8464,10 +8478,10 @@
         <v>82</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>478</v>
+        <v>471</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>82</v>
@@ -8475,10 +8489,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8489,7 +8503,7 @@
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>82</v>
@@ -8498,19 +8512,23 @@
         <v>82</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>191</v>
+        <v>479</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="N55" s="2"/>
-      <c r="O55" s="2"/>
+        <v>480</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>482</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
       </c>
@@ -8558,19 +8576,19 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>193</v>
+        <v>478</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>194</v>
+        <v>261</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>82</v>
@@ -8582,10 +8600,10 @@
         <v>82</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>82</v>
+        <v>483</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>195</v>
+        <v>484</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>82</v>
@@ -8593,21 +8611,21 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>154</v>
+        <v>82</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>82</v>
@@ -8619,17 +8637,15 @@
         <v>82</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>141</v>
+        <v>190</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -8678,19 +8694,19 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>82</v>
+        <v>194</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>147</v>
+        <v>82</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>82</v>
@@ -8713,14 +8729,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>201</v>
+        <v>154</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8733,26 +8749,24 @@
         <v>82</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K57" t="s" s="2">
         <v>141</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="O57" t="s" s="2">
-        <v>158</v>
-      </c>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>82</v>
       </c>
@@ -8800,7 +8814,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8827,7 +8841,7 @@
         <v>82</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>139</v>
+        <v>195</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>82</v>
@@ -8835,45 +8849,45 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>82</v>
+        <v>201</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="J58" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>243</v>
+        <v>141</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>484</v>
+        <v>202</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>485</v>
+        <v>203</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>486</v>
+        <v>157</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>258</v>
+        <v>158</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -8898,13 +8912,13 @@
         <v>82</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>366</v>
+        <v>82</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>487</v>
+        <v>82</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>488</v>
+        <v>82</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>82</v>
@@ -8922,34 +8936,34 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>483</v>
+        <v>204</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>261</v>
+        <v>82</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>106</v>
+        <v>147</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>263</v>
+        <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>489</v>
+        <v>82</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>265</v>
+        <v>82</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>215</v>
+        <v>139</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>82</v>
@@ -8957,10 +8971,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8968,7 +8982,7 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="G59" t="s" s="2">
         <v>94</v>
@@ -8983,19 +8997,19 @@
         <v>95</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="N59" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="L59" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>493</v>
-      </c>
       <c r="O59" t="s" s="2">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -9020,13 +9034,13 @@
         <v>82</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>82</v>
+        <v>371</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>82</v>
+        <v>492</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>82</v>
+        <v>493</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>82</v>
@@ -9044,16 +9058,16 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="AH59" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>82</v>
+        <v>261</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>106</v>
@@ -9062,19 +9076,19 @@
         <v>82</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>82</v>
+        <v>263</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>494</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>330</v>
+        <v>265</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>331</v>
+        <v>215</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>332</v>
+        <v>82</v>
       </c>
     </row>
     <row r="60" hidden="true">
@@ -9102,22 +9116,22 @@
         <v>82</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>243</v>
+        <v>496</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>497</v>
+        <v>325</v>
       </c>
       <c r="N60" t="s" s="2">
         <v>498</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9142,13 +9156,13 @@
         <v>82</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>259</v>
+        <v>82</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>338</v>
+        <v>82</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>339</v>
+        <v>82</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>82</v>
@@ -9187,35 +9201,35 @@
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>82</v>
+        <v>499</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>139</v>
+        <v>331</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>82</v>
+        <v>333</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>343</v>
+        <v>82</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>82</v>
@@ -9230,16 +9244,16 @@
         <v>243</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>344</v>
+        <v>501</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>345</v>
+        <v>502</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>346</v>
+        <v>503</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9267,10 +9281,10 @@
         <v>259</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -9288,13 +9302,13 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>82</v>
@@ -9309,28 +9323,28 @@
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>350</v>
+        <v>82</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>351</v>
+        <v>139</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>353</v>
+        <v>82</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>82</v>
+        <v>348</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9349,19 +9363,19 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>83</v>
+        <v>243</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>501</v>
+        <v>349</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>502</v>
+        <v>350</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>410</v>
+        <v>351</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>411</v>
+        <v>352</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>82</v>
@@ -9386,13 +9400,13 @@
         <v>82</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>82</v>
+        <v>259</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>82</v>
+        <v>353</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>82</v>
+        <v>354</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>82</v>
@@ -9410,7 +9424,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9431,20 +9445,142 @@
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>82</v>
+        <v>355</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>413</v>
+        <v>356</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>414</v>
+        <v>357</v>
       </c>
       <c r="AP62" t="s" s="2">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="63" hidden="true">
+      <c r="A63" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="P63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AO63" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AP63" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP62">
+  <autoFilter ref="A1:AP63">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9454,7 +9590,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI61">
+  <conditionalFormatting sqref="A2:AI62">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/StructureDefinition-specific-finding-observation-profile.xlsx
+++ b/StructureDefinition-specific-finding-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T14:48:08+00:00</t>
+    <t>2026-06-03T14:50:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1084,7 +1084,7 @@
     <t>Coded finding value, such as mTICI score or atrial fibrillation/flutter status</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/ValueSet/specific-finding-value-codeableconcept-vs</t>
+    <t>http://tecnomod-um.org/ValueSet/atrial-fibrillation-or-flutter-vs</t>
   </si>
   <si>
     <t>Observation.dataAbsentReason</t>
@@ -1975,7 +1975,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="54.6171875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="60.96875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="59.41796875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
@@ -5906,7 +5906,7 @@
         <v>82</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>259</v>
+        <v>118</v>
       </c>
       <c r="Y33" s="2"/>
       <c r="Z33" t="s" s="2">

--- a/StructureDefinition-specific-finding-observation-profile.xlsx
+++ b/StructureDefinition-specific-finding-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T14:50:23+00:00</t>
+    <t>2026-06-08T09:55:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-specific-finding-observation-profile.xlsx
+++ b/StructureDefinition-specific-finding-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T09:55:23+00:00</t>
+    <t>2026-06-08T10:51:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-specific-finding-observation-profile.xlsx
+++ b/StructureDefinition-specific-finding-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T10:51:55+00:00</t>
+    <t>2026-06-08T11:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-specific-finding-observation-profile.xlsx
+++ b/StructureDefinition-specific-finding-observation-profile.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$72</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2445" uniqueCount="508">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2793" uniqueCount="567">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T11:21:15+00:00</t>
+    <t>2026-06-11T11:47:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Observation profile for specific clinical, imaging or procedural findings including mTICI, bleeding volume, carotid stenosis, occlusion and atrial fibrillation/flutter.</t>
+    <t>Observation profile for specific stroke-related clinical, imaging and procedural findings including mTICI, bleeding volume, carotid stenosis, artery occlusion, atrial fibrillation/flutter and post-treatment findings.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -282,7 +282,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().ofType(canonical) | %resource.descendants().ofType(uri) | %resource.descendants().ofType(url))) or descendants().where(reference = '#').exists() or descendants().where(ofType(canonical) = '#').exists() or descendants().where(ofType(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.component.code is the same as Observation.code, then Observation.value SHALL NOT be present (the Observation.component.value[x] holds the value). {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}obs-8:bodyStructure SHALL only be present if Observation.bodySite is not present {bodySite.exists() implies bodyStructure.empty()}mtici-value-must-use-mtici-score-vs:If Observation.code is mTICI, valueCodeableConcept must belong to MTiciScoreVS. {code.coding.where(system = 'http://tecnomod-um.org/CodeSystem/specific-finding-cs' and code = 'mtici').exists().not() or value.ofType(CodeableConcept).memberOf('http://tecnomod-um.org/ValueSet/mtici-score-vs')}af-flutter-value-must-use-af-flutter-vs:If Observation.code is atrial fibrillation/flutter, valueCodeableConcept must belong to AtrialFibrillationOrFlutterVS. {code.coding.where(system = 'http://tecnomod-um.org/CodeSystem/specific-finding-cs' and code = 'atrial-fibrillation-flutter').exists().not() or value.ofType(CodeableConcept).memberOf('http://tecnomod-um.org/ValueSet/atrial-fibrillation-or-flutter-vs')}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().ofType(canonical) | %resource.descendants().ofType(uri) | %resource.descendants().ofType(url))) or descendants().where(reference = '#').exists() or descendants().where(ofType(canonical) = '#').exists() or descendants().where(ofType(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.component.code is the same as Observation.code, then Observation.value SHALL NOT be present (the Observation.component.value[x] holds the value). {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}obs-8:bodyStructure SHALL only be present if Observation.bodySite is not present {bodySite.exists() implies bodyStructure.empty()}specific-finding-must-have-result:A specific finding observation should have either a value or a dataAbsentReason. {value.exists() or dataAbsentReason.exists()}mtici-value-must-use-mtici-score-vs:If Observation.code is mTICI, valueCodeableConcept must belong to MTiciScoreVS. {code.coding.where(system = 'http://tecnomod-um.org/CodeSystem/mtici-code-cs' and code = 'mTICI').exists().not() or (value.ofType(CodeableConcept).exists() and value.ofType(CodeableConcept).memberOf('http://tecnomod-um.org/ValueSet/mtici-score-vs'))}blood-volume-must-be-quantity-ml:If Observation.code is blood volume, valueQuantity must be expressed in UCUM milliliters. {code.coding.where(system = 'http://snomed.info/sct' and code = '16086006').exists().not() or (value.ofType(Quantity).exists() and value.ofType(Quantity).system = 'http://unitsofmeasure.org' and value.ofType(Quantity).code = 'mL')}carotid-stenosis-value-rule:If Observation.code is carotid stenosis, the value must be either a boolean presence/absence value or a coded carotid stenosis level. {code.coding.where(system = 'http://snomed.info/sct' and (code = '64586002' or code = '787044009')).exists().not() or value.ofType(boolean).exists() or value.ofType(CodeableConcept).memberOf('http://tecnomod-um.org/ValueSet/carotid-stenosis-level-vs')}artery-occlusion-must-have-bodystructure:If Observation.code is artery occlusion, valueBoolean must be true and bodyStructure must be present. {code.coding.where(system = 'http://snomed.info/sct' and code = '2929001').exists().not() or (value.ofType(boolean) = true and bodyStructure.exists())}af-flutter-value-must-use-af-flutter-vs:If Observation.code is atrial fibrillation/flutter status, valueCodeableConcept must belong to AtrialFibrillationOrFlutterVS. {code.coding.where(system = 'http://tecnomod-um.org/CodeSystem/specific-finding-cs' and code = 'atrial-fibrillation-flutter').exists().not() or (value.ofType(CodeableConcept).exists() and value.ofType(CodeableConcept).memberOf('http://tecnomod-um.org/ValueSet/atrial-fibrillation-or-flutter-vs'))}hemorrhagic-transformation-value-rule:If Observation.code is hemorrhagic transformation, the value must be either a boolean presence/absence value or a coded hemorrhagic transformation type. {code.coding.where(system = 'http://snomed.info/sct' and code = '230706003').exists().not() or value.ofType(boolean).exists() or value.ofType(CodeableConcept).memberOf('http://tecnomod-um.org/ValueSet/hemorrhagic-transformation-type-vs')}</t>
   </si>
   <si>
     <t>Event</t>
@@ -784,7 +784,7 @@
 </t>
   </si>
   <si>
-    <t>Classification of  type of observation</t>
+    <t>Observation category, such as exam, procedure or laboratory</t>
   </si>
   <si>
     <t>A code that classifies the general type of observation being made.</t>
@@ -818,7 +818,7 @@
 </t>
   </si>
   <si>
-    <t>Specific stroke finding</t>
+    <t>Specific stroke-related finding</t>
   </si>
   <si>
     <t>Describes what was observed. Sometimes this is called the observation "name".</t>
@@ -1032,7 +1032,7 @@
   </si>
   <si>
     <t>Quantity
-CodeableConceptbooleaninteger</t>
+CodeableConceptboolean</t>
   </si>
   <si>
     <t>Finding value</t>
@@ -1059,6 +1059,9 @@
 </t>
   </si>
   <si>
+    <t>closed</t>
+  </si>
+  <si>
     <t>obs-7
 obs-6</t>
   </si>
@@ -1075,16 +1078,194 @@
     <t>363714003 |Interprets|</t>
   </si>
   <si>
+    <t>Observation.value[x]:valueBoolean</t>
+  </si>
+  <si>
+    <t>valueBoolean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>Presence or absence of the finding</t>
+  </si>
+  <si>
     <t>Observation.value[x]:valueCodeableConcept</t>
   </si>
   <si>
     <t>valueCodeableConcept</t>
   </si>
   <si>
-    <t>Coded finding value, such as mTICI score or atrial fibrillation/flutter status</t>
-  </si>
-  <si>
-    <t>http://tecnomod-um.org/ValueSet/atrial-fibrillation-or-flutter-vs</t>
+    <t>Coded finding value, such as mTICI score, AF/flutter status, carotid stenosis level or hemorrhagic transformation type</t>
+  </si>
+  <si>
+    <t>http://tecnomod-um.org/ValueSet/specific-finding-value-vs</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueQuantity</t>
+  </si>
+  <si>
+    <t>valueQuantity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantity
+</t>
+  </si>
+  <si>
+    <t>Quantitative finding value, such as bleeding volume</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueQuantity.id</t>
+  </si>
+  <si>
+    <t>Observation.value[x].id</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueQuantity.extension</t>
+  </si>
+  <si>
+    <t>Observation.value[x].extension</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueQuantity.value</t>
+  </si>
+  <si>
+    <t>Observation.value[x].value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">decimal
+</t>
+  </si>
+  <si>
+    <t>Numerical value (with implicit precision)</t>
+  </si>
+  <si>
+    <t>The value of the measured amount. The value includes an implicit precision in the presentation of the value.</t>
+  </si>
+  <si>
+    <t>The implicit precision in the value should always be honored. Monetary values have their own rules for handling precision (refer to standard accounting text books).</t>
+  </si>
+  <si>
+    <t>Precision is handled implicitly in almost all cases of measurement.</t>
+  </si>
+  <si>
+    <t>Quantity.value</t>
+  </si>
+  <si>
+    <t>SN.2  / CQ - N/A</t>
+  </si>
+  <si>
+    <t>PQ.value, CO.value, MO.value, IVL.high or IVL.low depending on the value</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueQuantity.comparator</t>
+  </si>
+  <si>
+    <t>Observation.value[x].comparator</t>
+  </si>
+  <si>
+    <t>&lt; | &lt;= | &gt;= | &gt; | ad - how to understand the value</t>
+  </si>
+  <si>
+    <t>How the value should be understood and represented - whether the actual value is greater or less than the stated value due to measurement issues; e.g. if the comparator is "&lt;" , then the real value is &lt; stated value.</t>
+  </si>
+  <si>
+    <t>Need a framework for handling measures where the value is &lt;5ug/L or &gt;400mg/L due to the limitations of measuring methodology.</t>
+  </si>
+  <si>
+    <t>If there is no comparator, then there is no modification of the value</t>
+  </si>
+  <si>
+    <t>How the Quantity should be understood and represented.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/quantity-comparator|5.0.0</t>
+  </si>
+  <si>
+    <t>Quantity.comparator</t>
+  </si>
+  <si>
+    <t>SN.1  / CQ.1</t>
+  </si>
+  <si>
+    <t>IVL properties</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueQuantity.unit</t>
+  </si>
+  <si>
+    <t>Observation.value[x].unit</t>
+  </si>
+  <si>
+    <t>Unit representation</t>
+  </si>
+  <si>
+    <t>A human-readable form of the unit.</t>
+  </si>
+  <si>
+    <t>There are many representations for units of measure and in many contexts, particular representations are fixed and required. I.e. mcg for micrograms.</t>
+  </si>
+  <si>
+    <t>Quantity.unit</t>
+  </si>
+  <si>
+    <t>(see OBX.6 etc.) / CQ.2</t>
+  </si>
+  <si>
+    <t>PQ.unit</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueQuantity.system</t>
+  </si>
+  <si>
+    <t>Observation.value[x].system</t>
+  </si>
+  <si>
+    <t>System that defines coded unit form</t>
+  </si>
+  <si>
+    <t>The identification of the system that provides the coded form of the unit.</t>
+  </si>
+  <si>
+    <t>Need to know the system that defines the coded form of the unit.</t>
+  </si>
+  <si>
+    <t>Quantity.system</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qty-3
+</t>
+  </si>
+  <si>
+    <t>CO.codeSystem, PQ.translation.codeSystem</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueQuantity.code</t>
+  </si>
+  <si>
+    <t>Observation.value[x].code</t>
+  </si>
+  <si>
+    <t>Coded form of the unit</t>
+  </si>
+  <si>
+    <t>A computer processable form of the unit in some unit representation system.</t>
+  </si>
+  <si>
+    <t>The preferred system is UCUM, but SNOMED CT can also be used (for customary units) or ISO 4217 for currency.  The context of use may additionally require a code from a particular system.</t>
+  </si>
+  <si>
+    <t>Need a computable form of the unit that is fixed across all forms. UCUM provides this for quantities, but SNOMED CT provides many units of interest.</t>
+  </si>
+  <si>
+    <t>Quantity.code</t>
+  </si>
+  <si>
+    <t>PQ.code, MO.currency, PQ.translation.code</t>
   </si>
   <si>
     <t>Observation.dataAbsentReason</t>
@@ -1181,7 +1362,7 @@
     <t>Observation.bodySite</t>
   </si>
   <si>
-    <t>Observed body part</t>
+    <t>Anatomical site when a simple coded body site is sufficient</t>
   </si>
   <si>
     <t>Indicates the site on the subject's body where the observation was made (i.e. the target site).</t>
@@ -1222,7 +1403,7 @@
 </t>
   </si>
   <si>
-    <t>Anatomical structure associated with the finding</t>
+    <t>Patient-specific anatomical structure associated with the finding</t>
   </si>
   <si>
     <t>Indicates the body structure on the subject's body where the observation was made (i.e. the target site).</t>
@@ -1947,7 +2128,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP63"/>
+  <dimension ref="A1:AP72"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="40.0234375" customWidth="true" bestFit="true"/>
@@ -1978,7 +2159,7 @@
     <col min="26" max="26" width="59.41796875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="35.16796875" customWidth="true" bestFit="true" hidden="true"/>
@@ -4764,7 +4945,7 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>81</v>
@@ -5803,7 +5984,7 @@
         <v>82</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>145</v>
+        <v>329</v>
       </c>
       <c r="AF32" t="s" s="2">
         <v>322</v>
@@ -5815,7 +5996,7 @@
         <v>94</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>106</v>
@@ -5827,27 +6008,27 @@
         <v>82</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>322</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D33" t="s" s="2">
         <v>82</v>
@@ -5860,7 +6041,7 @@
         <v>94</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>82</v>
@@ -5869,10 +6050,10 @@
         <v>95</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>243</v>
+        <v>337</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="M33" t="s" s="2">
         <v>325</v>
@@ -5906,11 +6087,13 @@
         <v>82</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="Y33" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z33" t="s" s="2">
-        <v>337</v>
+        <v>82</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>82</v>
@@ -5937,7 +6120,7 @@
         <v>94</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>106</v>
@@ -5949,26 +6132,28 @@
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="C34" s="2"/>
+        <v>322</v>
+      </c>
+      <c r="C34" t="s" s="2">
+        <v>340</v>
+      </c>
       <c r="D34" t="s" s="2">
         <v>82</v>
       </c>
@@ -5980,28 +6165,28 @@
         <v>94</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="K34" t="s" s="2">
         <v>243</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>340</v>
+        <v>325</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>341</v>
+        <v>326</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>342</v>
+        <v>327</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -6028,11 +6213,9 @@
       <c r="X34" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="Y34" t="s" s="2">
-        <v>343</v>
-      </c>
+      <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>82</v>
@@ -6050,7 +6233,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>338</v>
+        <v>322</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6059,7 +6242,7 @@
         <v>94</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>345</v>
+        <v>330</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>106</v>
@@ -6071,59 +6254,61 @@
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>82</v>
+        <v>331</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>139</v>
+        <v>332</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>82</v>
+        <v>334</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="C35" s="2"/>
+        <v>322</v>
+      </c>
+      <c r="C35" t="s" s="2">
+        <v>344</v>
+      </c>
       <c r="D35" t="s" s="2">
-        <v>348</v>
+        <v>82</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>243</v>
+        <v>345</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>350</v>
+        <v>325</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>351</v>
+        <v>326</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>352</v>
+        <v>327</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -6148,13 +6333,13 @@
         <v>82</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>259</v>
+        <v>82</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>353</v>
+        <v>82</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>354</v>
+        <v>82</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>82</v>
@@ -6172,16 +6357,16 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>347</v>
+        <v>322</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>82</v>
+        <v>330</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>106</v>
@@ -6193,24 +6378,24 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>355</v>
+        <v>331</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>356</v>
+        <v>332</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>357</v>
+        <v>333</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>358</v>
+        <v>334</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>359</v>
+        <v>347</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>359</v>
+        <v>348</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6221,7 +6406,7 @@
         <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>82</v>
@@ -6233,20 +6418,16 @@
         <v>82</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>360</v>
+        <v>96</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>361</v>
+        <v>191</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>364</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>82</v>
       </c>
@@ -6294,19 +6475,19 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>359</v>
+        <v>193</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>82</v>
+        <v>194</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>82</v>
@@ -6318,10 +6499,10 @@
         <v>82</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>365</v>
+        <v>82</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>366</v>
+        <v>195</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>82</v>
@@ -6329,21 +6510,21 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>367</v>
+        <v>349</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>367</v>
+        <v>350</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>82</v>
@@ -6355,16 +6536,16 @@
         <v>82</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>243</v>
+        <v>141</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>368</v>
+        <v>197</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>369</v>
+        <v>198</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>370</v>
+        <v>157</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6390,43 +6571,43 @@
         <v>82</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>371</v>
+        <v>82</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>372</v>
+        <v>82</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>373</v>
+        <v>82</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>82</v>
+        <v>144</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>82</v>
+        <v>351</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>82</v>
+        <v>145</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>367</v>
+        <v>199</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>374</v>
+        <v>82</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>106</v>
+        <v>147</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>82</v>
@@ -6435,24 +6616,24 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>375</v>
+        <v>82</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>376</v>
+        <v>82</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>377</v>
+        <v>195</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>378</v>
+        <v>82</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>379</v>
+        <v>352</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>379</v>
+        <v>353</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6460,7 +6641,7 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>94</v>
@@ -6472,21 +6653,23 @@
         <v>82</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>380</v>
+        <v>354</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>381</v>
+        <v>355</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>382</v>
+        <v>356</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="O38" s="2"/>
+        <v>357</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>358</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
       </c>
@@ -6534,7 +6717,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>379</v>
+        <v>359</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6543,7 +6726,7 @@
         <v>94</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>374</v>
+        <v>82</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>106</v>
@@ -6558,10 +6741,10 @@
         <v>82</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>82</v>
+        <v>360</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>377</v>
+        <v>361</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>82</v>
@@ -6569,10 +6752,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>384</v>
+        <v>362</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>384</v>
+        <v>363</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6589,30 +6772,30 @@
         <v>82</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>243</v>
+        <v>114</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>385</v>
+        <v>364</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>387</v>
-      </c>
+        <v>365</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>388</v>
+        <v>366</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q39" s="2"/>
+      <c r="Q39" t="s" s="2">
+        <v>367</v>
+      </c>
       <c r="R39" t="s" s="2">
         <v>82</v>
       </c>
@@ -6632,13 +6815,13 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>371</v>
+        <v>118</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>389</v>
+        <v>368</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>390</v>
+        <v>369</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
@@ -6656,7 +6839,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>384</v>
+        <v>370</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6680,21 +6863,21 @@
         <v>82</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>391</v>
+        <v>371</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>392</v>
+        <v>372</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
-        <v>393</v>
+        <v>373</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>393</v>
+        <v>374</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6708,27 +6891,27 @@
         <v>94</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>394</v>
+        <v>190</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>395</v>
+        <v>375</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="O40" s="2"/>
+        <v>376</v>
+      </c>
+      <c r="N40" s="2"/>
+      <c r="O40" t="s" s="2">
+        <v>377</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>82</v>
       </c>
@@ -6776,7 +6959,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>393</v>
+        <v>378</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6788,7 +6971,7 @@
         <v>82</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>398</v>
+        <v>106</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>82</v>
@@ -6797,24 +6980,24 @@
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>399</v>
+        <v>82</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>400</v>
+        <v>379</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>401</v>
+        <v>380</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>402</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
-        <v>403</v>
+        <v>381</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>403</v>
+        <v>382</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6822,33 +7005,33 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>404</v>
+        <v>108</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>405</v>
+        <v>383</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="O41" s="2"/>
+        <v>384</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" t="s" s="2">
+        <v>385</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
       </c>
@@ -6896,7 +7079,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>403</v>
+        <v>386</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6905,7 +7088,7 @@
         <v>94</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>82</v>
+        <v>387</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>106</v>
@@ -6917,24 +7100,24 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>408</v>
+        <v>82</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>409</v>
+        <v>379</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>410</v>
+        <v>388</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>411</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
-        <v>412</v>
+        <v>389</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>412</v>
+        <v>390</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6942,34 +7125,34 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>186</v>
+        <v>114</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>413</v>
+        <v>391</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>414</v>
+        <v>392</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>415</v>
+        <v>393</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>416</v>
+        <v>394</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -7018,19 +7201,19 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>412</v>
+        <v>395</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>82</v>
+        <v>387</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>417</v>
+        <v>106</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>82</v>
@@ -7042,10 +7225,10 @@
         <v>82</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>418</v>
+        <v>379</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>419</v>
+        <v>396</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>82</v>
@@ -7053,10 +7236,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>420</v>
+        <v>397</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>420</v>
+        <v>397</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7079,16 +7262,20 @@
         <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>190</v>
+        <v>243</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>191</v>
+        <v>398</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
+        <v>399</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>401</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
       </c>
@@ -7112,13 +7299,13 @@
         <v>82</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>82</v>
+        <v>259</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>82</v>
+        <v>402</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>82</v>
+        <v>403</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>82</v>
@@ -7136,7 +7323,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>193</v>
+        <v>397</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7145,10 +7332,10 @@
         <v>94</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>194</v>
+        <v>404</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>82</v>
@@ -7160,10 +7347,10 @@
         <v>82</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>195</v>
+        <v>405</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>82</v>
@@ -7171,14 +7358,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>421</v>
+        <v>406</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>421</v>
+        <v>406</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>154</v>
+        <v>407</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7197,18 +7384,20 @@
         <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>141</v>
+        <v>243</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>197</v>
+        <v>408</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>198</v>
+        <v>409</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="O44" s="2"/>
+        <v>410</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>411</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
       </c>
@@ -7232,13 +7421,13 @@
         <v>82</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>82</v>
+        <v>259</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>82</v>
+        <v>412</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>82</v>
+        <v>413</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>82</v>
@@ -7256,7 +7445,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>199</v>
+        <v>406</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7268,7 +7457,7 @@
         <v>82</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>147</v>
+        <v>106</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>82</v>
@@ -7277,28 +7466,28 @@
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>82</v>
+        <v>414</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>82</v>
+        <v>415</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>195</v>
+        <v>416</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>82</v>
+        <v>417</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>201</v>
+        <v>82</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7311,25 +7500,25 @@
         <v>82</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>141</v>
+        <v>419</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>202</v>
+        <v>420</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>203</v>
+        <v>421</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>157</v>
+        <v>422</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>158</v>
+        <v>423</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>82</v>
@@ -7378,7 +7567,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>204</v>
+        <v>418</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7390,7 +7579,7 @@
         <v>82</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>147</v>
+        <v>106</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>82</v>
@@ -7402,21 +7591,21 @@
         <v>82</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>82</v>
+        <v>424</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>139</v>
+        <v>425</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7430,7 +7619,7 @@
         <v>94</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>82</v>
@@ -7439,15 +7628,17 @@
         <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>424</v>
+        <v>243</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>428</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>429</v>
+      </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>82</v>
@@ -7472,13 +7663,13 @@
         <v>82</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>82</v>
+        <v>430</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>82</v>
+        <v>431</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>82</v>
+        <v>432</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>82</v>
@@ -7496,7 +7687,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7505,7 +7696,7 @@
         <v>94</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>106</v>
@@ -7517,24 +7708,24 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>82</v>
+        <v>434</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>418</v>
+        <v>435</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>82</v>
+        <v>437</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7548,7 +7739,7 @@
         <v>94</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>82</v>
@@ -7557,15 +7748,17 @@
         <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>424</v>
+        <v>439</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>441</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>442</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>82</v>
@@ -7614,7 +7807,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7623,7 +7816,7 @@
         <v>94</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>106</v>
@@ -7638,10 +7831,10 @@
         <v>82</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>418</v>
+        <v>82</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>82</v>
@@ -7649,10 +7842,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7678,13 +7871,17 @@
         <v>243</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>434</v>
+        <v>444</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+        <v>445</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>447</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
       </c>
@@ -7708,13 +7905,13 @@
         <v>82</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>259</v>
+        <v>430</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
@@ -7732,7 +7929,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7756,10 +7953,10 @@
         <v>82</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>418</v>
+        <v>450</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>438</v>
+        <v>451</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>82</v>
@@ -7767,10 +7964,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>439</v>
+        <v>452</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>439</v>
+        <v>452</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7793,20 +7990,18 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>243</v>
+        <v>453</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>440</v>
+        <v>454</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>441</v>
+        <v>455</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>443</v>
-      </c>
+        <v>456</v>
+      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>82</v>
       </c>
@@ -7830,13 +8025,13 @@
         <v>82</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>248</v>
+        <v>82</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>444</v>
+        <v>82</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>445</v>
+        <v>82</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
@@ -7854,7 +8049,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>439</v>
+        <v>452</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7866,7 +8061,7 @@
         <v>82</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>106</v>
+        <v>457</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>82</v>
@@ -7875,24 +8070,24 @@
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>446</v>
+        <v>458</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>447</v>
+        <v>459</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>357</v>
+        <v>460</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>82</v>
+        <v>461</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>448</v>
+        <v>462</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>448</v>
+        <v>462</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7903,7 +8098,7 @@
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>82</v>
@@ -7915,20 +8110,18 @@
         <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>243</v>
+        <v>463</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>449</v>
+        <v>464</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>450</v>
+        <v>465</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>452</v>
-      </c>
+        <v>466</v>
+      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>82</v>
       </c>
@@ -7952,13 +8145,13 @@
         <v>82</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>371</v>
+        <v>82</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>453</v>
+        <v>82</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>454</v>
+        <v>82</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>82</v>
@@ -7976,13 +8169,13 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>448</v>
+        <v>462</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>82</v>
@@ -7997,24 +8190,24 @@
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>446</v>
+        <v>467</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>447</v>
+        <v>468</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>357</v>
+        <v>469</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>82</v>
+        <v>470</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>455</v>
+        <v>471</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>455</v>
+        <v>471</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8025,7 +8218,7 @@
         <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>82</v>
@@ -8037,17 +8230,19 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>456</v>
+        <v>186</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>457</v>
+        <v>472</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>473</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>474</v>
+      </c>
       <c r="O51" t="s" s="2">
-        <v>459</v>
+        <v>475</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -8096,19 +8291,19 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>455</v>
+        <v>471</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>106</v>
+        <v>476</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>82</v>
@@ -8120,10 +8315,10 @@
         <v>82</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>82</v>
+        <v>477</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>460</v>
+        <v>478</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>82</v>
@@ -8131,10 +8326,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8157,13 +8352,13 @@
         <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>462</v>
+        <v>190</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>463</v>
+        <v>191</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>464</v>
+        <v>192</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8214,7 +8409,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>461</v>
+        <v>193</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8223,10 +8418,10 @@
         <v>94</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>427</v>
+        <v>194</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>82</v>
@@ -8238,10 +8433,10 @@
         <v>82</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>418</v>
+        <v>82</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>465</v>
+        <v>195</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>82</v>
@@ -8249,14 +8444,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>466</v>
+        <v>480</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>466</v>
+        <v>480</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8272,19 +8467,19 @@
         <v>82</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>467</v>
+        <v>141</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>468</v>
+        <v>197</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>469</v>
+        <v>198</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>470</v>
+        <v>157</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8334,7 +8529,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>466</v>
+        <v>199</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8346,7 +8541,7 @@
         <v>82</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>106</v>
+        <v>147</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>82</v>
@@ -8358,10 +8553,10 @@
         <v>82</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>471</v>
+        <v>82</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>82</v>
@@ -8369,14 +8564,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>82</v>
+        <v>201</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8389,24 +8584,26 @@
         <v>82</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="J54" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>473</v>
+        <v>141</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>474</v>
+        <v>202</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>475</v>
+        <v>203</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="O54" s="2"/>
+        <v>157</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
       </c>
@@ -8454,7 +8651,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>472</v>
+        <v>204</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8466,7 +8663,7 @@
         <v>82</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>106</v>
+        <v>147</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>82</v>
@@ -8478,10 +8675,10 @@
         <v>82</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>471</v>
+        <v>82</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>477</v>
+        <v>139</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>82</v>
@@ -8489,10 +8686,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8503,7 +8700,7 @@
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>82</v>
@@ -8512,23 +8709,19 @@
         <v>82</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>186</v>
+        <v>483</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>482</v>
-      </c>
+        <v>485</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>82</v>
       </c>
@@ -8576,16 +8769,16 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>261</v>
+        <v>486</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>106</v>
@@ -8600,10 +8793,10 @@
         <v>82</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>82</v>
@@ -8611,10 +8804,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8637,13 +8830,13 @@
         <v>82</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>190</v>
+        <v>483</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>191</v>
+        <v>489</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>192</v>
+        <v>490</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8694,7 +8887,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>193</v>
+        <v>488</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8703,10 +8896,10 @@
         <v>94</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>194</v>
+        <v>486</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>82</v>
@@ -8718,10 +8911,10 @@
         <v>82</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>82</v>
+        <v>477</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>195</v>
+        <v>491</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>82</v>
@@ -8729,21 +8922,21 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>154</v>
+        <v>82</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>82</v>
@@ -8755,17 +8948,15 @@
         <v>82</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>141</v>
+        <v>243</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>197</v>
+        <v>493</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>494</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>82</v>
@@ -8790,13 +8981,13 @@
         <v>82</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>82</v>
+        <v>259</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>82</v>
+        <v>495</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>82</v>
+        <v>496</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>82</v>
@@ -8814,19 +9005,19 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>199</v>
+        <v>492</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>147</v>
+        <v>106</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>82</v>
@@ -8838,10 +9029,10 @@
         <v>82</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>82</v>
+        <v>477</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>195</v>
+        <v>497</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>82</v>
@@ -8849,45 +9040,45 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>487</v>
+        <v>498</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>487</v>
+        <v>498</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>201</v>
+        <v>82</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>141</v>
+        <v>243</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>202</v>
+        <v>499</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>203</v>
+        <v>500</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>157</v>
+        <v>501</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>158</v>
+        <v>502</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -8912,13 +9103,13 @@
         <v>82</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>82</v>
+        <v>248</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>82</v>
+        <v>503</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>82</v>
+        <v>504</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>82</v>
@@ -8936,19 +9127,19 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>204</v>
+        <v>498</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>147</v>
+        <v>106</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>82</v>
@@ -8957,13 +9148,13 @@
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>82</v>
+        <v>505</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>82</v>
+        <v>506</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>139</v>
+        <v>416</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>82</v>
@@ -8971,10 +9162,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>488</v>
+        <v>507</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>488</v>
+        <v>507</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8982,10 +9173,10 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>82</v>
@@ -8994,22 +9185,22 @@
         <v>82</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K59" t="s" s="2">
         <v>243</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>489</v>
+        <v>508</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>490</v>
+        <v>509</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>491</v>
+        <v>510</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>258</v>
+        <v>511</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -9034,13 +9225,13 @@
         <v>82</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>371</v>
+        <v>430</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>492</v>
+        <v>512</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>493</v>
+        <v>513</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>82</v>
@@ -9058,16 +9249,16 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>488</v>
+        <v>507</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>261</v>
+        <v>82</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>106</v>
@@ -9076,16 +9267,16 @@
         <v>82</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>263</v>
+        <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>494</v>
+        <v>505</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>265</v>
+        <v>506</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>215</v>
+        <v>416</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>82</v>
@@ -9093,10 +9284,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>495</v>
+        <v>514</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>495</v>
+        <v>514</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9116,22 +9307,20 @@
         <v>82</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>496</v>
+        <v>515</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>497</v>
+        <v>516</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>498</v>
-      </c>
+        <v>517</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>327</v>
+        <v>518</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9180,7 +9369,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>495</v>
+        <v>514</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9201,24 +9390,24 @@
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>499</v>
+        <v>82</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>331</v>
+        <v>82</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>332</v>
+        <v>519</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>333</v>
+        <v>82</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>500</v>
+        <v>520</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>500</v>
+        <v>520</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9241,20 +9430,16 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>243</v>
+        <v>521</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>501</v>
+        <v>522</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>342</v>
-      </c>
+        <v>523</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>82</v>
       </c>
@@ -9278,13 +9463,13 @@
         <v>82</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>259</v>
+        <v>82</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>343</v>
+        <v>82</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>344</v>
+        <v>82</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -9302,7 +9487,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>500</v>
+        <v>520</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9311,7 +9496,7 @@
         <v>94</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>82</v>
+        <v>486</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>106</v>
@@ -9326,10 +9511,10 @@
         <v>82</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>139</v>
+        <v>477</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>346</v>
+        <v>524</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>82</v>
@@ -9337,14 +9522,14 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>504</v>
+        <v>525</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>504</v>
+        <v>525</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>348</v>
+        <v>82</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9360,23 +9545,21 @@
         <v>82</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>243</v>
+        <v>526</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>349</v>
+        <v>527</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>350</v>
+        <v>528</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>352</v>
-      </c>
+        <v>529</v>
+      </c>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>82</v>
       </c>
@@ -9400,13 +9583,13 @@
         <v>82</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>259</v>
+        <v>82</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>353</v>
+        <v>82</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>354</v>
+        <v>82</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>82</v>
@@ -9424,7 +9607,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>504</v>
+        <v>525</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9445,24 +9628,24 @@
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>355</v>
+        <v>82</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>356</v>
+        <v>530</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>357</v>
+        <v>209</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>358</v>
+        <v>82</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>505</v>
+        <v>531</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>505</v>
+        <v>531</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9482,23 +9665,21 @@
         <v>82</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>83</v>
+        <v>532</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>506</v>
+        <v>533</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>507</v>
+        <v>534</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>416</v>
-      </c>
+        <v>535</v>
+      </c>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>82</v>
       </c>
@@ -9546,7 +9727,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>505</v>
+        <v>531</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9570,17 +9751,1109 @@
         <v>82</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>418</v>
+        <v>530</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>419</v>
+        <v>536</v>
       </c>
       <c r="AP63" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="P64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="AO64" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="AP64" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AP65" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AP66" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="67" hidden="true">
+      <c r="A67" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="P67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AP67" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="68" hidden="true">
+      <c r="A68" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="P68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AO68" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AP68" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="P69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="AO69" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="AP69" t="s" s="2">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="70" hidden="true">
+      <c r="A70" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="P70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AP70" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="P71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AP71" t="s" s="2">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="72" hidden="true">
+      <c r="A72" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="P72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AO72" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AP72" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP63">
+  <autoFilter ref="A1:AP72">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9590,7 +10863,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI62">
+  <conditionalFormatting sqref="A2:AI71">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/StructureDefinition-specific-finding-observation-profile.xlsx
+++ b/StructureDefinition-specific-finding-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T11:47:40+00:00</t>
+    <t>2026-06-11T14:44:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -282,7 +282,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().ofType(canonical) | %resource.descendants().ofType(uri) | %resource.descendants().ofType(url))) or descendants().where(reference = '#').exists() or descendants().where(ofType(canonical) = '#').exists() or descendants().where(ofType(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.component.code is the same as Observation.code, then Observation.value SHALL NOT be present (the Observation.component.value[x] holds the value). {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}obs-8:bodyStructure SHALL only be present if Observation.bodySite is not present {bodySite.exists() implies bodyStructure.empty()}specific-finding-must-have-result:A specific finding observation should have either a value or a dataAbsentReason. {value.exists() or dataAbsentReason.exists()}mtici-value-must-use-mtici-score-vs:If Observation.code is mTICI, valueCodeableConcept must belong to MTiciScoreVS. {code.coding.where(system = 'http://tecnomod-um.org/CodeSystem/mtici-code-cs' and code = 'mTICI').exists().not() or (value.ofType(CodeableConcept).exists() and value.ofType(CodeableConcept).memberOf('http://tecnomod-um.org/ValueSet/mtici-score-vs'))}blood-volume-must-be-quantity-ml:If Observation.code is blood volume, valueQuantity must be expressed in UCUM milliliters. {code.coding.where(system = 'http://snomed.info/sct' and code = '16086006').exists().not() or (value.ofType(Quantity).exists() and value.ofType(Quantity).system = 'http://unitsofmeasure.org' and value.ofType(Quantity).code = 'mL')}carotid-stenosis-value-rule:If Observation.code is carotid stenosis, the value must be either a boolean presence/absence value or a coded carotid stenosis level. {code.coding.where(system = 'http://snomed.info/sct' and (code = '64586002' or code = '787044009')).exists().not() or value.ofType(boolean).exists() or value.ofType(CodeableConcept).memberOf('http://tecnomod-um.org/ValueSet/carotid-stenosis-level-vs')}artery-occlusion-must-have-bodystructure:If Observation.code is artery occlusion, valueBoolean must be true and bodyStructure must be present. {code.coding.where(system = 'http://snomed.info/sct' and code = '2929001').exists().not() or (value.ofType(boolean) = true and bodyStructure.exists())}af-flutter-value-must-use-af-flutter-vs:If Observation.code is atrial fibrillation/flutter status, valueCodeableConcept must belong to AtrialFibrillationOrFlutterVS. {code.coding.where(system = 'http://tecnomod-um.org/CodeSystem/specific-finding-cs' and code = 'atrial-fibrillation-flutter').exists().not() or (value.ofType(CodeableConcept).exists() and value.ofType(CodeableConcept).memberOf('http://tecnomod-um.org/ValueSet/atrial-fibrillation-or-flutter-vs'))}hemorrhagic-transformation-value-rule:If Observation.code is hemorrhagic transformation, the value must be either a boolean presence/absence value or a coded hemorrhagic transformation type. {code.coding.where(system = 'http://snomed.info/sct' and code = '230706003').exists().not() or value.ofType(boolean).exists() or value.ofType(CodeableConcept).memberOf('http://tecnomod-um.org/ValueSet/hemorrhagic-transformation-type-vs')}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().ofType(canonical) | %resource.descendants().ofType(uri) | %resource.descendants().ofType(url))) or descendants().where(reference = '#').exists() or descendants().where(ofType(canonical) = '#').exists() or descendants().where(ofType(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.component.code is the same as Observation.code, then Observation.value SHALL NOT be present (the Observation.component.value[x] holds the value). {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}obs-8:bodyStructure SHALL only be present if Observation.bodySite is not present {bodySite.exists() implies bodyStructure.empty()}specific-finding-must-have-result:A specific finding observation should have either a value or a dataAbsentReason. {value.exists() or dataAbsentReason.exists()}mtici-value-must-use-mtici-score-vs:If Observation.code is mTICI, valueCodeableConcept must belong to MTiciScoreVS. {code.coding.where(system = 'http://tecnomod-um.org/CodeSystem/mtici-code-cs' and code = 'mTICI').exists().not() or (value.ofType(CodeableConcept).exists() and value.ofType(CodeableConcept).memberOf('http://tecnomod-um.org/ValueSet/mtici-score-vs'))}blood-volume-must-be-quantity-ml:If Observation.code is blood volume, valueQuantity must be expressed in UCUM milliliters. {code.coding.where(system = 'http://snomed.info/sct' and code = '16086006').exists().not() or (value.ofType(Quantity).exists() and value.ofType(Quantity).system = 'https://ucum.org/ucum' and value.ofType(Quantity).code = 'mL')}carotid-stenosis-value-rule:If Observation.code is carotid stenosis, the value must be either a boolean presence/absence value or a coded carotid stenosis level. {code.coding.where(system = 'http://snomed.info/sct' and (code = '64586002' or code = '787044009')).exists().not() or value.ofType(boolean).exists() or value.ofType(CodeableConcept).memberOf('http://tecnomod-um.org/ValueSet/carotid-stenosis-level-vs')}artery-occlusion-must-have-bodystructure:If Observation.code is artery occlusion, valueBoolean must be true and bodyStructure must be present. {code.coding.where(system = 'http://snomed.info/sct' and code = '2929001').exists().not() or (value.ofType(boolean) = true and bodyStructure.exists())}af-flutter-value-must-use-af-flutter-vs:If Observation.code is atrial fibrillation/flutter status, valueCodeableConcept must belong to AtrialFibrillationOrFlutterVS. {code.coding.where(system = 'http://tecnomod-um.org/CodeSystem/specific-finding-cs' and code = 'atrial-fibrillation-flutter').exists().not() or (value.ofType(CodeableConcept).exists() and value.ofType(CodeableConcept).memberOf('http://tecnomod-um.org/ValueSet/atrial-fibrillation-or-flutter-vs'))}hemorrhagic-transformation-value-rule:If Observation.code is hemorrhagic transformation, the value must be either a boolean presence/absence value or a coded hemorrhagic transformation type. {code.coding.where(system = 'http://snomed.info/sct' and code = '230706003').exists().not() or value.ofType(boolean).exists() or value.ofType(CodeableConcept).memberOf('http://tecnomod-um.org/ValueSet/hemorrhagic-transformation-type-vs')}</t>
   </si>
   <si>
     <t>Event</t>

--- a/StructureDefinition-specific-finding-observation-profile.xlsx
+++ b/StructureDefinition-specific-finding-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:44:28+00:00</t>
+    <t>2026-06-12T09:34:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-specific-finding-observation-profile.xlsx
+++ b/StructureDefinition-specific-finding-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T09:34:13+00:00</t>
+    <t>2026-07-01T13:43:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-specific-finding-observation-profile.xlsx
+++ b/StructureDefinition-specific-finding-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T13:43:23+00:00</t>
+    <t>2026-07-09T09:09:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-specific-finding-observation-profile.xlsx
+++ b/StructureDefinition-specific-finding-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T09:09:43+00:00</t>
+    <t>2026-07-13T09:21:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-specific-finding-observation-profile.xlsx
+++ b/StructureDefinition-specific-finding-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T09:21:26+00:00</t>
+    <t>2026-07-13T09:30:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-specific-finding-observation-profile.xlsx
+++ b/StructureDefinition-specific-finding-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T09:30:27+00:00</t>
+    <t>2026-07-14T07:23:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-specific-finding-observation-profile.xlsx
+++ b/StructureDefinition-specific-finding-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-14T07:23:58+00:00</t>
+    <t>2026-07-17T09:40:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-specific-finding-observation-profile.xlsx
+++ b/StructureDefinition-specific-finding-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T09:40:30+00:00</t>
+    <t>2026-07-21T08:04:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-specific-finding-observation-profile.xlsx
+++ b/StructureDefinition-specific-finding-observation-profile.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/StructureDefinition/specific-finding-observation-profile</t>
+    <t>http://qualityregistry.org/StructureDefinition/specific-finding-observation-profile</t>
   </si>
   <si>
     <t>Version</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T08:04:16+00:00</t>
+    <t>2026-08-31T09:17:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Tecnomod / Universidad de Murcia (http://tecnomod-um.org)</t>
+    <t>Tecnomod / Universidad de Murcia (http://qualityregistry.org)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -117,7 +117,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/StructureDefinition/base-stroke-observation</t>
+    <t>http://qualityregistry.org/StructureDefinition/base-stroke-observation</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -282,7 +282,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().ofType(canonical) | %resource.descendants().ofType(uri) | %resource.descendants().ofType(url))) or descendants().where(reference = '#').exists() or descendants().where(ofType(canonical) = '#').exists() or descendants().where(ofType(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.component.code is the same as Observation.code, then Observation.value SHALL NOT be present (the Observation.component.value[x] holds the value). {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}obs-8:bodyStructure SHALL only be present if Observation.bodySite is not present {bodySite.exists() implies bodyStructure.empty()}specific-finding-must-have-result:A specific finding observation should have either a value or a dataAbsentReason. {value.exists() or dataAbsentReason.exists()}mtici-value-must-use-mtici-score-vs:If Observation.code is mTICI, valueCodeableConcept must belong to MTiciScoreVS. {code.coding.where(system = 'http://tecnomod-um.org/CodeSystem/mtici-code-cs' and code = 'mTICI').exists().not() or (value.ofType(CodeableConcept).exists() and value.ofType(CodeableConcept).memberOf('http://tecnomod-um.org/ValueSet/mtici-score-vs'))}blood-volume-must-be-quantity-ml:If Observation.code is blood volume, valueQuantity must be expressed in UCUM milliliters. {code.coding.where(system = 'http://snomed.info/sct' and code = '16086006').exists().not() or (value.ofType(Quantity).exists() and value.ofType(Quantity).system = 'https://ucum.org/ucum' and value.ofType(Quantity).code = 'mL')}carotid-stenosis-value-rule:If Observation.code is carotid stenosis, the value must be either a boolean presence/absence value or a coded carotid stenosis level. {code.coding.where(system = 'http://snomed.info/sct' and (code = '64586002' or code = '787044009')).exists().not() or value.ofType(boolean).exists() or value.ofType(CodeableConcept).memberOf('http://tecnomod-um.org/ValueSet/carotid-stenosis-level-vs')}artery-occlusion-must-have-bodystructure:If Observation.code is artery occlusion, valueBoolean must be true and bodyStructure must be present. {code.coding.where(system = 'http://snomed.info/sct' and code = '2929001').exists().not() or (value.ofType(boolean) = true and bodyStructure.exists())}af-flutter-value-must-use-af-flutter-vs:If Observation.code is atrial fibrillation/flutter status, valueCodeableConcept must belong to AtrialFibrillationOrFlutterVS. {code.coding.where(system = 'http://tecnomod-um.org/CodeSystem/specific-finding-cs' and code = 'atrial-fibrillation-flutter').exists().not() or (value.ofType(CodeableConcept).exists() and value.ofType(CodeableConcept).memberOf('http://tecnomod-um.org/ValueSet/atrial-fibrillation-or-flutter-vs'))}hemorrhagic-transformation-value-rule:If Observation.code is hemorrhagic transformation, the value must be either a boolean presence/absence value or a coded hemorrhagic transformation type. {code.coding.where(system = 'http://snomed.info/sct' and code = '230706003').exists().not() or value.ofType(boolean).exists() or value.ofType(CodeableConcept).memberOf('http://tecnomod-um.org/ValueSet/hemorrhagic-transformation-type-vs')}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().ofType(canonical) | %resource.descendants().ofType(uri) | %resource.descendants().ofType(url))) or descendants().where(reference = '#').exists() or descendants().where(ofType(canonical) = '#').exists() or descendants().where(ofType(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.component.code is the same as Observation.code, then Observation.value SHALL NOT be present (the Observation.component.value[x] holds the value). {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}obs-8:bodyStructure SHALL only be present if Observation.bodySite is not present {bodySite.exists() implies bodyStructure.empty()}specific-finding-must-have-result:A specific finding observation should have either a value or a dataAbsentReason. {value.exists() or dataAbsentReason.exists()}mtici-value-must-use-mtici-score-vs:If Observation.code is mTICI, valueCodeableConcept must belong to MTiciScoreVS. {code.coding.where(system = 'http://qualityregistry.org/CodeSystem/mtici-code-cs' and code = 'mTICI').exists().not() or (value.ofType(CodeableConcept).exists() and value.ofType(CodeableConcept).memberOf('http://qualityregistry.org/ValueSet/mtici-score-vs'))}blood-volume-must-be-quantity-ml:If Observation.code is blood volume, valueQuantity must be expressed in UCUM milliliters. {code.coding.where(system = 'http://snomed.info/sct' and code = '16086006').exists().not() or (value.ofType(Quantity).exists() and value.ofType(Quantity).system = 'https://ucum.org/ucum' and value.ofType(Quantity).code = 'mL')}carotid-stenosis-value-rule:If Observation.code is carotid stenosis, the value must be either a boolean presence/absence value or a coded carotid stenosis level. {code.coding.where(system = 'http://snomed.info/sct' and (code = '64586002' or code = '787044009')).exists().not() or value.ofType(boolean).exists() or value.ofType(CodeableConcept).memberOf('http://qualityregistry.org/ValueSet/carotid-stenosis-level-vs')}artery-occlusion-must-have-bodystructure:If Observation.code is artery occlusion, valueBoolean must be true and bodyStructure must be present. {code.coding.where(system = 'http://snomed.info/sct' and code = '2929001').exists().not() or (value.ofType(boolean) = true and bodyStructure.exists())}af-flutter-value-must-use-af-flutter-vs:If Observation.code is atrial fibrillation/flutter status, valueCodeableConcept must belong to AtrialFibrillationOrFlutterVS. {code.coding.where(system = 'http://qualityregistry.org/CodeSystem/specific-finding-cs' and code = 'atrial-fibrillation-flutter').exists().not() or (value.ofType(CodeableConcept).exists() and value.ofType(CodeableConcept).memberOf('http://qualityregistry.org/ValueSet/atrial-fibrillation-or-flutter-vs'))}hemorrhagic-transformation-value-rule:If Observation.code is hemorrhagic transformation, the value must be either a boolean presence/absence value or a coded hemorrhagic transformation type. {code.coding.where(system = 'http://snomed.info/sct' and code = '230706003').exists().not() or value.ofType(boolean).exists() or value.ofType(CodeableConcept).memberOf('http://qualityregistry.org/ValueSet/hemorrhagic-transformation-type-vs')}</t>
   </si>
   <si>
     <t>Event</t>
@@ -485,7 +485,7 @@
     <t>observationTimingContext</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://tecnomod-um.org/StructureDefinition/observation-timing-context-ext}
+    <t xml:space="preserve">Extension {http://qualityregistry.org/StructureDefinition/observation-timing-context-ext}
 </t>
   </si>
   <si>
@@ -833,7 +833,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/ValueSet/specific-finding-vs</t>
+    <t>http://qualityregistry.org/ValueSet/specific-finding-vs</t>
   </si>
   <si>
     <t xml:space="preserve">obs-7
@@ -858,7 +858,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://tecnomod-um.org/StructureDefinition/resq-patient-profile)
+    <t xml:space="preserve">Reference(http://qualityregistry.org/StructureDefinition/resq-patient-profile)
 </t>
   </si>
   <si>
@@ -912,7 +912,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://tecnomod-um.org/StructureDefinition/stroke-encounter-profile)
+    <t xml:space="preserve">Reference(http://qualityregistry.org/StructureDefinition/stroke-encounter-profile)
 </t>
   </si>
   <si>
@@ -1100,7 +1100,7 @@
     <t>Coded finding value, such as mTICI score, AF/flutter status, carotid stenosis level or hemorrhagic transformation type</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/ValueSet/specific-finding-value-vs</t>
+    <t>http://qualityregistry.org/ValueSet/specific-finding-value-vs</t>
   </si>
   <si>
     <t>Observation.value[x]:valueQuantity</t>
@@ -1399,7 +1399,7 @@
     <t>Observation.bodyStructure</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://tecnomod-um.org/StructureDefinition/resq-body-structure-profile)
+    <t xml:space="preserve">Reference(http://qualityregistry.org/StructureDefinition/resq-body-structure-profile)
 </t>
   </si>
   <si>

--- a/StructureDefinition-specific-finding-observation-profile.xlsx
+++ b/StructureDefinition-specific-finding-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T09:17:06+00:00</t>
+    <t>2026-08-31T10:08:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-specific-finding-observation-profile.xlsx
+++ b/StructureDefinition-specific-finding-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T10:08:26+00:00</t>
+    <t>2026-09-04T09:44:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-specific-finding-observation-profile.xlsx
+++ b/StructureDefinition-specific-finding-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T09:44:50+00:00</t>
+    <t>2026-09-04T10:11:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
